--- a/PayRoll/ImportFormatFiles/DeductionImportFormat.xlsx
+++ b/PayRoll/ImportFormatFiles/DeductionImportFormat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMC Projects\VanitaPayroll\PayRoll\ImportFormatFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB87D447-A833-4AB5-B774-EC470BB4C1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2598C994-7815-4008-B7E7-C5492D20A0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>EMPCODE</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>NAME</t>
+  </si>
+  <si>
+    <t>Expenses</t>
   </si>
 </sst>
 </file>
@@ -401,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="13.3984375" customWidth="1"/>
@@ -411,7 +414,7 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="13.15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="13.15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
